--- a/data/asteroides_decurrens/intersect_decurrens_window_proteins_function_candidate.xlsx
+++ b/data/asteroides_decurrens/intersect_decurrens_window_proteins_function_candidate.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gowustl-my.sharepoint.com/personal/wen-hsi_kuo_wustl_edu/Documents/MOBOT/MOBOT_Boltonia/data/asteroides_decurrens/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_4A0EFED48F79A8D366075C52F37BD272FAC78E96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0031812-5F2A-F74F-965D-37C5E9DD5091}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_4A0EFED48F79A8D366075C52F37BD272FAC78E96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDFF6438-52E9-4741-B5D5-4FBDD693C52B}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="500" windowWidth="37780" windowHeight="18280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="500" windowWidth="37780" windowHeight="18280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="138">
   <si>
     <t>qseqid</t>
   </si>
@@ -422,6 +423,21 @@
   </si>
   <si>
     <t>Supports differentiation in elongation and canopy response strategies associated with different light regimes in floodplain vs upland habitats.</t>
+  </si>
+  <si>
+    <t>Gene_ID</t>
+  </si>
+  <si>
+    <t>Gene_Symbol</t>
+  </si>
+  <si>
+    <t>Protein_Name</t>
+  </si>
+  <si>
+    <t>Uniprot_Accession</t>
+  </si>
+  <si>
+    <t>Potential_Function</t>
   </si>
 </sst>
 </file>
@@ -1502,4 +1518,327 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8AC32D-5A6C-4244-A246-4B719C6BFF69}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="40.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.1640625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>